--- a/docs/ui-post-eight/KyPost-Council.xlsx
+++ b/docs/ui-post-eight/KyPost-Council.xlsx
@@ -5077,6 +5077,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/docs/ui-post-eight/KyPost-Council.xlsx
+++ b/docs/ui-post-eight/KyPost-Council.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Progression" sheetId="3" r:id="rId3"/>
     <sheet name="Spreads" sheetId="4" r:id="rId4"/>
     <sheet name="Notes" sheetId="5" r:id="rId5"/>
+    <sheet name="Delivery" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -11385,4 +11386,107 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repository</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Busnes-app/KyPost-Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">url</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://github.com/Busnes-app/KyPost-Server/pull/489</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">branch</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui/post-eight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ui_source</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50bbbff5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b6852d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">open; whole-repository current-head CI/security and R2 primary scores pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">merge_deploy_authorized</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">False</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/ui-post-eight/KyPost-Council.xlsx
+++ b/docs/ui-post-eight/KyPost-Council.xlsx
@@ -9908,17 +9908,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Combined exact</t>
+          <t xml:space="preserve">Historical combined exact (not gate)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rounded</t>
+          <t xml:space="preserve">Opus rounded</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accepted</t>
+          <t xml:space="preserve">Accepted by current rule</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2</t>
+          <t xml:space="preserve">6.8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9977,12 +9977,44 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">7.6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">True</t>
+          <t xml:space="preserve">False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
         </is>
       </c>
     </row>
@@ -22376,7 +22408,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same-set Claude/Sol quality mean, half-up to one decimal; &gt;=8.0 accepts. Brand is separate; raw scores/satisfaction retained.</t>
+          <t xml:space="preserve">Opus overall current-round quality mean, half-up to one decimal; &gt;=8.0 accepts. Sol is independent. Prior combined-score acceptance is superseded; historical reports are immutable. Brand is separate.</t>
         </is>
       </c>
     </row>
@@ -22455,7 +22487,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://github.com/Busnes-app/KyPost-Server/pull/489</t>
+          <t xml:space="preserve">Pending follow-up PR</t>
         </is>
       </c>
     </row>
@@ -22467,7 +22499,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui/post-eight</t>
+          <t xml:space="preserve">ui/post-control-consistency</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50bbbff5</t>
+          <t xml:space="preserve">2ff40cc2394d1bab8cf14935ba6b219a5f28b8f1</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22535,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">open; visual progression accepted8.0; whole-repository current-head CI/security pending</t>
+          <t xml:space="preserve">reopened under clarified Opus-only gate; round3 primary reviews pending</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22559,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">2 complete,3pending</t>
         </is>
       </c>
     </row>
@@ -22539,7 +22571,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">513/64</t>
+          <t xml:space="preserve">513/64 (historical, not gate)</t>
         </is>
       </c>
     </row>
@@ -22551,7 +22583,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.0</t>
+          <t xml:space="preserve">8.0 (historical, not gate)</t>
         </is>
       </c>
     </row>
@@ -22563,7 +22595,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">True</t>
+          <t xml:space="preserve">False</t>
         </is>
       </c>
     </row>
@@ -22576,6 +22608,30 @@
       <c r="B13" t="inlineStr">
         <is>
           <t xml:space="preserve">Unused; both primaries not independently satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">opus_rounded</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.6; previous captured set</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">previous_pr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://github.com/Busnes-app/KyPost-Server/pull/489</t>
         </is>
       </c>
     </row>

--- a/docs/ui-post-eight/KyPost-Council.xlsx
+++ b/docs/ui-post-eight/KyPost-Council.xlsx
@@ -44540,7 +44540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"round": 4, "raw_reports": {"opus-round4.json": "fc9763aefe34753e8fa12601e85ec7f663b16d459c62c20bf16d43e53276c095", "opus-round4.md": "ad917b57e27b922c06751e988b7da8439c23fe93c22c4ed007e22c56ddbd15da", "sol-round4.json": "9e6ebf14198418c5b755dd6671f6ad33eae0ee14094092157b6b76b8830cceb8", "sol-round4.md": "df1a598f2bd5d6f23eecbc19a88f31fe8e4abed926115cf96bbc09e7c7530f90"}, "source_ui": "558761afa10560a5ba9522e6d7603dbf2a17ccfd", "frozen_evidence": "f53e76ced2506284b393baffbc3f181ba4549543", "membership": "Both report sets match all32 stage06 originals; hashes and exact weighted totals independently reproduced.", "progression": {"opus_exact": "1277/160", "opus_decimal": "7.98125", "opus_rounded": "8.0", "accepted": true, "sol_exact": "1369/160", "sol_decimal": "8.55625", "rule": "Opus current overall only, half-up to0.1. No pooling with Sol, brand or history."}, "independent_satisfaction": {"opus": {"satisfied": true, "genuinely_satisfied": true}, "sol": {"satisfied": true, "genuinely_satisfied": true}}, "spread_audit": {"dimensions_ge_2": 2, "entries": [{"file": "screenshots/kypost-06-after-contacts-mobile-dark.png", "dimension": "density_layout", "opus": 6, "sol": 8}, {"file": "screenshots/kypost-06-after-contacts-mobile-light.png", "dimension": "density_layout", "opus": 6, "sol": 8}], "inspection": "Parent re-opened both stage06 phone contacts originals individually at native resolution. Approximately137px rows split name, email and action text across different left edges; the search hint clips. Opus6 vsSol8 density is a valid judgment spread, retained unchanged. No broken view or progression veto.", "resolution": "Retain both raw vectors and findings; no averaged replacement or cosmetic round."}, "freeze_integrity": {"opus": "Verified persisted checks/opus-r4-freeze.json bytes against publisher hash. Quality vectors, observations, totals, brand vectors/observations/N/A exclusions all unchanged. Final brand records add mean_exact_fraction only (all32); raw full-vector digest therefore differs if derived metadata is included.", "opus_frozen_file_sha256": "8fe9a11f471f7fc4efe0557de120ad6313a26a5748472248ec4ee1ab1dc85a97", "sol": "Full files-array digest reproduces050708ca86dab5500f6bf13595fa14bf7ff4b006d6c08a40a6689ae66c8958e0."}, "drift": "Opus raw mean rises0.09375; Sol raw mean falls0.1. Both disclose variance on unchanged images. Never use variance-adjusted estimates as progression scores.", "remaining_findings": ["Phone contacts row density/alignment, clipped search hint and repeated count.", "Contact-editor photo helper placement and disclosure spacing.", "Phone bulk toolbar wrap; optional navigation-label consistency."], "limitations": ["Everyday-user initial views only; full behavior/roles/states/all named themes/assistive-tech/competitive gates remain untested.", "Opus live supplement uses a different browser/DPR and does not replace scored originals.", "Current-head whole-repository hostedCI and security review remain pending."], "gemini": "Advisory pending; launched only after both primaries genuinely satisfied. Acceptance is already decided.", "dox_pass": "Evidence records and existing exporter only. Owning AGENTS and parent indexes intentionally unchanged: ownership, structure and progression contracts are unchanged."}</t>
+          <t xml:space="preserve">{"round": 4, "raw_reports": {"opus-round4.json": "fc9763aefe34753e8fa12601e85ec7f663b16d459c62c20bf16d43e53276c095", "opus-round4.md": "ad917b57e27b922c06751e988b7da8439c23fe93c22c4ed007e22c56ddbd15da", "sol-round4.json": "9e6ebf14198418c5b755dd6671f6ad33eae0ee14094092157b6b76b8830cceb8", "sol-round4.md": "df1a598f2bd5d6f23eecbc19a88f31fe8e4abed926115cf96bbc09e7c7530f90"}, "source_ui": "558761afa10560a5ba9522e6d7603dbf2a17ccfd", "frozen_evidence": "f53e76ced2506284b393baffbc3f181ba4549543", "membership": "Both report sets match all32 stage06 originals; hashes and exact weighted totals independently reproduced.", "progression": {"opus_exact": "1277/160", "opus_decimal": "7.98125", "opus_rounded": "8.0", "accepted": true, "sol_exact": "1369/160", "sol_decimal": "8.55625", "rule": "Opus current overall only, half-up to0.1. No pooling with Sol, brand or history."}, "independent_satisfaction": {"opus": {"satisfied": true, "genuinely_satisfied": true}, "sol": {"satisfied": true, "genuinely_satisfied": true}}, "spread_audit": {"dimensions_ge_2": 2, "entries": [{"file": "screenshots/kypost-06-after-contacts-mobile-dark.png", "dimension": "density_layout", "opus": 6, "sol": 8}, {"file": "screenshots/kypost-06-after-contacts-mobile-light.png", "dimension": "density_layout", "opus": 6, "sol": 8}], "inspection": "Parent re-opened both stage06 phone contacts originals individually at native resolution. Approximately137px rows split name, email and action text across different left edges; the search hint clips. Opus6 vsSol8 density is a valid judgment spread, retained unchanged. No broken view or progression veto.", "resolution": "Retain both raw vectors and findings; no averaged replacement or cosmetic round."}, "freeze_integrity": {"opus": "Verified persisted checks/opus-r4-freeze.json bytes against publisher hash. Quality vectors, observations, totals, brand vectors/observations/N/A exclusions all unchanged. Final brand records add mean_exact_fraction only (all32); raw full-vector digest therefore differs if derived metadata is included.", "opus_frozen_file_sha256": "8fe9a11f471f7fc4efe0557de120ad6313a26a5748472248ec4ee1ab1dc85a97", "sol": "Full files-array digest reproduces050708ca86dab5500f6bf13595fa14bf7ff4b006d6c08a40a6689ae66c8958e0."}, "drift": "Opus raw mean rises0.09375; Sol raw mean falls0.1. Both disclose variance on unchanged images. Never use variance-adjusted estimates as progression scores.", "remaining_findings": ["Phone contacts row density/alignment, clipped search hint and repeated count.", "Contact-editor photo helper placement and disclosure spacing.", "Phone bulk toolbar wrap; optional navigation-label consistency."], "limitations": ["Everyday-user initial views only; full behavior/roles/states/all named themes/assistive-tech/competitive gates remain untested.", "Opus live supplement uses a different browser/DPR and does not replace scored originals.", "Current-head whole-repository hostedCI and security review remain pending."], "gemini": "Unavailable: quota reached; no score", "dox_pass": "Evidence records and existing exporter only. Owning AGENTS and parent indexes intentionally unchanged: ownership, structure and progression contracts are unchanged."}</t>
         </is>
       </c>
     </row>
@@ -44679,7 +44679,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pending advisory</t>
+          <t xml:space="preserve">Unavailable: quota reached; no score</t>
         </is>
       </c>
     </row>
